--- a/Top100Songs_Filled.xlsx
+++ b/Top100Songs_Filled.xlsx
@@ -1387,7 +1387,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Prateek Kuhad - Co2 Live Across TWTLD Tour 2022</t>
+          <t>Co2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
